--- a/datos/2022-04-29 05 analisis desviaciones - Queso vaca.xlsx
+++ b/datos/2022-04-29 05 analisis desviaciones - Queso vaca.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/34bf2af71bbc2e43/Documentos/GitHub/master-queseria/website/datos/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1010" documentId="8_{296E09A7-40FA-4BA4-83C6-8A64E89513BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CB3C2F91-3F3A-433A-ADCA-6A7BAFF79813}"/>
+  <xr:revisionPtr revIDLastSave="1013" documentId="8_{296E09A7-40FA-4BA4-83C6-8A64E89513BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{95DF6A2A-5DE0-4E50-9FF4-E4F3EEA706FA}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="675" activeTab="3" xr2:uid="{6977E7F1-D64B-47FE-B2A7-D4E9B0399E18}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="675" activeTab="2" xr2:uid="{6977E7F1-D64B-47FE-B2A7-D4E9B0399E18}"/>
   </bookViews>
   <sheets>
     <sheet name="Datos" sheetId="8" r:id="rId1"/>
@@ -9344,8 +9344,7 @@
       </c>
       <c r="B2" s="31"/>
       <c r="C2" s="198">
-        <f>Datos!F6</f>
-        <v>10.71</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
@@ -9423,7 +9422,7 @@
       </c>
       <c r="B8" s="7">
         <f>B12/B15*1000</f>
-        <v>90.614164648273146</v>
+        <v>846.07063163653709</v>
       </c>
       <c r="C8" s="143">
         <f>Datos!F7</f>
@@ -9466,7 +9465,7 @@
       </c>
       <c r="B11" s="68">
         <f>B$4/B$19*C$2</f>
-        <v>3.5237319280915491</v>
+        <v>28.931597437487088</v>
       </c>
       <c r="C11" s="211">
         <f>Datos!F8</f>
@@ -9480,7 +9479,7 @@
       </c>
       <c r="B12" s="68">
         <f>C$2*B$5/B$20</f>
-        <v>3.0551505546751194</v>
+        <v>28.526148969889064</v>
       </c>
       <c r="C12" s="211">
         <f>Datos!F9</f>
@@ -9510,7 +9509,7 @@
       </c>
       <c r="B14" s="35">
         <f>B11/B12</f>
-        <v>1.1533742331288344</v>
+        <v>1.0142132212807975</v>
       </c>
       <c r="C14" s="35">
         <f>C11/C12</f>
@@ -9527,7 +9526,7 @@
       </c>
       <c r="C15" s="26">
         <f>C31*C2/C8</f>
-        <v>32.505882352941171</v>
+        <v>32.505882352941178</v>
       </c>
       <c r="I15" s="36"/>
     </row>
@@ -9541,7 +9540,7 @@
       </c>
       <c r="C16" s="26">
         <f>C30*C2/C8</f>
-        <v>35.599999999999994</v>
+        <v>35.6</v>
       </c>
       <c r="D16" s="95"/>
     </row>
@@ -9555,7 +9554,7 @@
       </c>
       <c r="C17" s="26">
         <f>C21/C18</f>
-        <v>32.747399999999999</v>
+        <v>305.76470588235298</v>
       </c>
       <c r="I17" s="5"/>
     </row>
@@ -9569,7 +9568,7 @@
       </c>
       <c r="C18" s="26">
         <f>(C5*1000/C15)/C20</f>
-        <v>7.9365079365079376</v>
+        <v>0.85</v>
       </c>
       <c r="I18" s="5"/>
     </row>
@@ -9578,12 +9577,11 @@
         <v>14</v>
       </c>
       <c r="B19" s="110">
-        <f>'Estandar Tecnico'!B11</f>
-        <v>0.85102955082742304</v>
+        <v>0.96779999999999999</v>
       </c>
       <c r="C19" s="25">
         <f>(C4*C2)/C11</f>
-        <v>0.91987078651685417</v>
+        <v>8.5888962326503648</v>
       </c>
       <c r="I19" s="5"/>
     </row>
@@ -9597,7 +9595,7 @@
       </c>
       <c r="C20" s="25">
         <f>C5*C2/C12</f>
-        <v>0.93029315960912062</v>
+        <v>8.686210640608035</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
@@ -9657,7 +9655,7 @@
       </c>
       <c r="C24" s="16">
         <f>C16-C17</f>
-        <v>2.8525999999999954</v>
+        <v>-270.16470588235296</v>
       </c>
       <c r="F24" s="38"/>
       <c r="I24" s="5"/>
@@ -9672,7 +9670,7 @@
       </c>
       <c r="C25" s="25">
         <f>C24/C16</f>
-        <v>8.0129213483145945E-2</v>
+        <v>-7.5888962326503639</v>
       </c>
       <c r="G25" s="5"/>
       <c r="H25" s="5"/>
@@ -9703,7 +9701,7 @@
       </c>
       <c r="C27" s="26">
         <f>C24-C26</f>
-        <v>2.8525999999999954</v>
+        <v>-270.16470588235296</v>
       </c>
       <c r="F27" s="5"/>
       <c r="G27" s="5"/>
@@ -9720,7 +9718,7 @@
       </c>
       <c r="C28" s="39">
         <f>C27/C16</f>
-        <v>8.0129213483145945E-2</v>
+        <v>-7.5888962326503639</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
@@ -9742,15 +9740,15 @@
       </c>
       <c r="B30" s="21">
         <f>B11/C2*1000</f>
-        <v>329.01325192264699</v>
+        <v>289.3159743748709</v>
       </c>
       <c r="C30" s="20">
         <f>C11/C2*1000</f>
-        <v>282.53968253968247</v>
+        <v>30.259999999999998</v>
       </c>
       <c r="D30" s="7">
         <f>(B11-C11)*B32</f>
-        <v>2.4510801242284255</v>
+        <v>127.57207525093366</v>
       </c>
       <c r="F30" s="150" t="s">
         <v>115</v>
@@ -9773,22 +9771,22 @@
       </c>
       <c r="B31" s="19">
         <f>B12/C2*1000</f>
-        <v>285.26148969889073</v>
+        <v>285.26148969889067</v>
       </c>
       <c r="C31" s="18">
         <f>C12/C2*1000</f>
-        <v>257.98319327731087</v>
+        <v>27.63</v>
       </c>
       <c r="D31" s="12">
         <f>(B12-C12)*B33</f>
-        <v>1.6593536996029252</v>
+        <v>146.3292671278555</v>
       </c>
       <c r="E31" t="s">
         <v>132</v>
       </c>
       <c r="F31" s="195">
         <f>B11</f>
-        <v>3.5237319280915491</v>
+        <v>28.931597437487088</v>
       </c>
       <c r="G31" s="195">
         <f>C11</f>
@@ -9796,11 +9794,11 @@
       </c>
       <c r="H31" s="195">
         <f>F31-G31</f>
-        <v>0.49773192809154931</v>
+        <v>25.905597437487089</v>
       </c>
       <c r="I31" s="195">
         <f>H31*B38</f>
-        <v>2.4510801242284255</v>
+        <v>127.57207525093366</v>
       </c>
       <c r="J31" s="5"/>
       <c r="K31" s="5"/>
@@ -9864,7 +9862,7 @@
       </c>
       <c r="F33" s="195">
         <f>B12</f>
-        <v>3.0551505546751194</v>
+        <v>28.526148969889064</v>
       </c>
       <c r="G33" s="195">
         <f>C12</f>
@@ -9872,11 +9870,11 @@
       </c>
       <c r="H33" s="195">
         <f>F33-G33</f>
-        <v>0.29215055467511952</v>
+        <v>25.763148969889066</v>
       </c>
       <c r="I33" s="195">
         <f>H33*B39</f>
-        <v>1.6593536996029252</v>
+        <v>146.3292671278555</v>
       </c>
       <c r="J33" s="5"/>
       <c r="K33" s="5"/>
@@ -9887,14 +9885,14 @@
       <c r="C34" s="22"/>
       <c r="D34" s="1">
         <f>SUM(D30:D33)</f>
-        <v>4.1104338238313503</v>
+        <v>273.9013423787892</v>
       </c>
       <c r="F34" s="195"/>
       <c r="G34" s="195"/>
       <c r="H34" s="195"/>
       <c r="I34" s="195">
         <f>SUM(I31:I33)</f>
-        <v>4.1104338238313503</v>
+        <v>273.9013423787892</v>
       </c>
       <c r="J34" s="5"/>
       <c r="K34" s="5"/>
@@ -9912,15 +9910,15 @@
       </c>
       <c r="B36" s="21">
         <f>(B11-B13)/C2*1000</f>
-        <v>329.01325192264699</v>
+        <v>289.3159743748709</v>
       </c>
       <c r="C36" s="21">
         <f>(C11-C13)/C2*1000</f>
-        <v>282.53968253968247</v>
+        <v>30.259999999999998</v>
       </c>
       <c r="D36" s="7">
         <f>((B36-C36)*B38*C2/1000)</f>
-        <v>2.4510801242284286</v>
+        <v>127.57207525093368</v>
       </c>
       <c r="F36" s="150" t="s">
         <v>115</v>
@@ -9943,22 +9941,22 @@
       </c>
       <c r="B37" s="19">
         <f>B12/C2*1000</f>
-        <v>285.26148969889073</v>
+        <v>285.26148969889067</v>
       </c>
       <c r="C37" s="18">
         <f>C12/C2*1000</f>
-        <v>257.98319327731087</v>
+        <v>27.63</v>
       </c>
       <c r="D37" s="12">
         <f>((B37-C37)*B39*C2/1000)</f>
-        <v>1.6593536996029292</v>
+        <v>146.3292671278555</v>
       </c>
       <c r="E37" t="s">
         <v>131</v>
       </c>
       <c r="F37" s="195">
         <f>(B11-B13)</f>
-        <v>3.5237319280915491</v>
+        <v>28.931597437487088</v>
       </c>
       <c r="G37" s="195">
         <f>C11-C13</f>
@@ -9966,11 +9964,11 @@
       </c>
       <c r="H37" s="195">
         <f>F37-G37</f>
-        <v>0.49773192809154931</v>
+        <v>25.905597437487089</v>
       </c>
       <c r="I37" s="195">
         <f>H37*B38</f>
-        <v>2.4510801242284255</v>
+        <v>127.57207525093366</v>
       </c>
       <c r="J37" s="5"/>
       <c r="K37" s="5"/>
@@ -9996,7 +9994,7 @@
       </c>
       <c r="F38" s="195">
         <f>B12</f>
-        <v>3.0551505546751194</v>
+        <v>28.526148969889064</v>
       </c>
       <c r="G38" s="195">
         <f>C12</f>
@@ -10004,11 +10002,11 @@
       </c>
       <c r="H38" s="195">
         <f>F38-G38</f>
-        <v>0.29215055467511952</v>
+        <v>25.763148969889066</v>
       </c>
       <c r="I38" s="195">
         <f>H38*B39</f>
-        <v>1.6593536996029252</v>
+        <v>146.3292671278555</v>
       </c>
       <c r="J38" s="5"/>
       <c r="K38" s="5"/>
@@ -10034,7 +10032,7 @@
       <c r="H39" s="195"/>
       <c r="I39" s="195">
         <f>SUM(I37:I38)</f>
-        <v>4.1104338238313503</v>
+        <v>273.9013423787892</v>
       </c>
       <c r="J39" s="5"/>
       <c r="K39" s="5"/>
@@ -10045,7 +10043,7 @@
       <c r="C40" s="9"/>
       <c r="D40" s="1">
         <f>SUM(D36:D39)</f>
-        <v>4.1104338238313574</v>
+        <v>273.9013423787892</v>
       </c>
       <c r="F40" s="5"/>
       <c r="G40" s="5"/>
@@ -10097,7 +10095,7 @@
       </c>
       <c r="B44" s="199">
         <f>B$4/B$19*C$2</f>
-        <v>3.5237319280915491</v>
+        <v>28.931597437487088</v>
       </c>
       <c r="C44" s="199">
         <f>(C$4/C$19)*C$2</f>
@@ -10105,7 +10103,7 @@
       </c>
       <c r="D44" s="200">
         <f>B44-C44</f>
-        <v>0.49773192809154931</v>
+        <v>25.905597437487089</v>
       </c>
       <c r="E44" s="201"/>
       <c r="F44" s="201"/>
@@ -10119,29 +10117,29 @@
       </c>
       <c r="B45" s="202">
         <f>B$4/B$19*C$2</f>
-        <v>3.5237319280915491</v>
+        <v>28.931597437487088</v>
       </c>
       <c r="C45" s="202">
         <f>(C$4/B$19)*C$2</f>
-        <v>3.2707783146821203</v>
+        <v>26.854722050010331</v>
       </c>
       <c r="D45" s="203">
         <f>B45-C45</f>
-        <v>0.25295361340942879</v>
+        <v>2.0768753874767576</v>
       </c>
       <c r="E45" s="204"/>
       <c r="F45" s="204">
         <f>D45</f>
-        <v>0.25295361340942879</v>
+        <v>2.0768753874767576</v>
       </c>
       <c r="G45" s="202"/>
       <c r="H45" s="202">
         <f t="shared" ref="H45:H47" si="0">F45*B$38</f>
-        <v>1.2456696851996436</v>
+        <v>10.227569692509586</v>
       </c>
       <c r="I45" s="203">
         <f t="shared" ref="I45:I47" si="1">SUM(G45:H45)</f>
-        <v>1.2456696851996436</v>
+        <v>10.227569692509586</v>
       </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.25">
@@ -10150,7 +10148,7 @@
       </c>
       <c r="B46" s="202">
         <f>B$4/B$19*C$2</f>
-        <v>3.5237319280915491</v>
+        <v>28.931597437487088</v>
       </c>
       <c r="C46" s="202">
         <f>(B$4/C$19)*C$2</f>
@@ -10158,21 +10156,21 @@
       </c>
       <c r="D46" s="203">
         <f>B46-C46</f>
-        <v>0.26370884228931768</v>
+        <v>25.671574351684857</v>
       </c>
       <c r="E46" s="204"/>
       <c r="F46" s="204">
         <f>D46</f>
-        <v>0.26370884228931768</v>
+        <v>25.671574351684857</v>
       </c>
       <c r="G46" s="202"/>
       <c r="H46" s="202">
         <f t="shared" si="0"/>
-        <v>1.2986337934900292</v>
+        <v>126.41962892019528</v>
       </c>
       <c r="I46" s="203">
         <f t="shared" si="1"/>
-        <v>1.2986337934900292</v>
+        <v>126.41962892019528</v>
       </c>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.25">
@@ -10183,21 +10181,21 @@
       <c r="C47" s="206"/>
       <c r="D47" s="207">
         <f>(B19-C19)*(B4-C4)*C2</f>
-        <v>-1.4819521648099535E-2</v>
+        <v>-15.318403427627237</v>
       </c>
       <c r="E47" s="208"/>
       <c r="F47" s="208">
         <f>D47</f>
-        <v>-1.4819521648099535E-2</v>
+        <v>-15.318403427627237</v>
       </c>
       <c r="G47" s="205"/>
       <c r="H47" s="205">
         <f t="shared" si="0"/>
-        <v>-7.2978711857014919E-2</v>
+        <v>-75.435454422894978</v>
       </c>
       <c r="I47" s="207">
         <f t="shared" si="1"/>
-        <v>-7.2978711857014919E-2</v>
+        <v>-75.435454422894978</v>
       </c>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.25">
@@ -10206,7 +10204,7 @@
       </c>
       <c r="B48" s="199">
         <f t="shared" ref="B48" si="2">C$2*B$5/B$20</f>
-        <v>3.0551505546751194</v>
+        <v>28.526148969889064</v>
       </c>
       <c r="C48" s="199">
         <f>C2*C5/C20</f>
@@ -10214,7 +10212,7 @@
       </c>
       <c r="D48" s="200">
         <f>B48-C48</f>
-        <v>0.29215055467511952</v>
+        <v>25.763148969889066</v>
       </c>
       <c r="E48" s="201"/>
       <c r="F48" s="201"/>
@@ -10228,29 +10226,29 @@
       </c>
       <c r="B49" s="202">
         <f t="shared" ref="B49:B50" si="3">C$2*B$5/B$20</f>
-        <v>3.0551505546751194</v>
+        <v>28.526148969889064</v>
       </c>
       <c r="C49" s="202">
         <f>C2*C5/B20</f>
-        <v>2.7156893819334393</v>
+        <v>25.356576862123614</v>
       </c>
       <c r="D49" s="203">
         <f>B49-C49</f>
-        <v>0.33946117274168008</v>
+        <v>3.1695721077654504</v>
       </c>
       <c r="E49" s="204">
         <f>D49</f>
-        <v>0.33946117274168008</v>
+        <v>3.1695721077654504</v>
       </c>
       <c r="F49" s="204"/>
       <c r="G49" s="202">
         <f>E49*B$39</f>
-        <v>1.9280680589049239</v>
+        <v>18.002502884266313</v>
       </c>
       <c r="H49" s="202"/>
       <c r="I49" s="203">
         <f>SUM(G49:H49)</f>
-        <v>1.9280680589049239</v>
+        <v>18.002502884266313</v>
       </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.25">
@@ -10259,7 +10257,7 @@
       </c>
       <c r="B50" s="202">
         <f t="shared" si="3"/>
-        <v>3.0551505546751194</v>
+        <v>28.526148969889064</v>
       </c>
       <c r="C50" s="202">
         <f>C2*B5/C20</f>
@@ -10267,21 +10265,21 @@
       </c>
       <c r="D50" s="203">
         <f>B50-C50</f>
-        <v>-5.3224445324880687E-2</v>
+        <v>25.417773969889065</v>
       </c>
       <c r="E50" s="204">
         <f>D50</f>
-        <v>-5.3224445324880687E-2</v>
+        <v>25.417773969889065</v>
       </c>
       <c r="F50" s="204"/>
       <c r="G50" s="202">
         <f t="shared" ref="G50:G51" si="4">E50*B$39</f>
-        <v>-0.30230365421474881</v>
+        <v>144.36760977403782</v>
       </c>
       <c r="H50" s="202"/>
       <c r="I50" s="203">
         <f t="shared" ref="I50:I51" si="5">SUM(G50:H50)</f>
-        <v>-0.30230365421474881</v>
+        <v>144.36760977403782</v>
       </c>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.25">
@@ -10292,21 +10290,21 @@
       <c r="C51" s="206"/>
       <c r="D51" s="205">
         <f>(B20-C20)*(B5-C5)*C2</f>
-        <v>5.2072578175895515E-3</v>
+        <v>-23.219131921824125</v>
       </c>
       <c r="E51" s="208">
         <f>D51</f>
-        <v>5.2072578175895515E-3</v>
+        <v>-23.219131921824125</v>
       </c>
       <c r="F51" s="208"/>
       <c r="G51" s="205">
         <f t="shared" si="4"/>
-        <v>2.9576129109226523E-2</v>
+        <v>-131.87978540342809</v>
       </c>
       <c r="H51" s="205"/>
       <c r="I51" s="207">
         <f t="shared" si="5"/>
-        <v>2.9576129109226523E-2</v>
+        <v>-131.87978540342809</v>
       </c>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.25">
@@ -10489,23 +10487,23 @@
       <c r="D58" s="199"/>
       <c r="E58" s="201">
         <f>SUM(E44:E54)</f>
-        <v>0.29144398523438897</v>
+        <v>5.3682141558303904</v>
       </c>
       <c r="F58" s="201">
         <f>SUM(F44:F54)</f>
-        <v>0.50184293405064695</v>
+        <v>12.430046311534378</v>
       </c>
       <c r="G58" s="199">
         <f>SUM(G44:G54)</f>
-        <v>1.6553405337994016</v>
+        <v>30.490327254876036</v>
       </c>
       <c r="H58" s="199">
         <f>SUM(H44:H54)</f>
-        <v>2.4713247668326579</v>
+        <v>61.211744189809892</v>
       </c>
       <c r="I58" s="200">
         <f>SUM(I44:I57)</f>
-        <v>4.1266653006320606</v>
+        <v>91.702071444685942</v>
       </c>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.25">
@@ -10520,7 +10518,7 @@
       </c>
       <c r="B61" s="210">
         <f>SUM(I45,I49)</f>
-        <v>3.1737377441045673</v>
+        <v>28.2300725767759</v>
       </c>
       <c r="D61" s="5"/>
     </row>
@@ -10530,7 +10528,7 @@
       </c>
       <c r="B62" s="202">
         <f>SUM(I46,I50)</f>
-        <v>0.99633013927528036</v>
+        <v>270.78723869423311</v>
       </c>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.25">
@@ -10548,7 +10546,7 @@
       </c>
       <c r="B64" s="202">
         <f>SUM(I47+I51+I57)</f>
-        <v>-4.3402582747788396E-2</v>
+        <v>-207.31523982632308</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
@@ -10557,7 +10555,7 @@
       </c>
       <c r="B65" s="205">
         <f>SUM(B61:B64)</f>
-        <v>4.1266653006320597</v>
+        <v>91.702071444685942</v>
       </c>
     </row>
   </sheetData>

--- a/datos/2022-04-29 05 analisis desviaciones - Queso vaca.xlsx
+++ b/datos/2022-04-29 05 analisis desviaciones - Queso vaca.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="1013" documentId="8_{296E09A7-40FA-4BA4-83C6-8A64E89513BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{95DF6A2A-5DE0-4E50-9FF4-E4F3EEA706FA}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="675" activeTab="2" xr2:uid="{6977E7F1-D64B-47FE-B2A7-D4E9B0399E18}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="675" xr2:uid="{6977E7F1-D64B-47FE-B2A7-D4E9B0399E18}"/>
   </bookViews>
   <sheets>
     <sheet name="Datos" sheetId="8" r:id="rId1"/>
